--- a/data/trans_camb/IP2002-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -1,16</t>
+          <t>-12,22; -1,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 3,04</t>
+          <t>-9,19; 3,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 6,51</t>
+          <t>-7,0; 5,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 3,61</t>
+          <t>-7,46; 3,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 1,9</t>
+          <t>-8,9; 1,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 5,77</t>
+          <t>-6,01; 5,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -0,27</t>
+          <t>-7,87; -0,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 0,36</t>
+          <t>-7,97; 0,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 4,02</t>
+          <t>-4,58; 3,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-94,19; -7,42</t>
+          <t>-100,0; -3,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,73; 75,94</t>
+          <t>-78,56; 77,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 118,73</t>
+          <t>-56,28; 100,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,57; 138,8</t>
+          <t>-77,0; 136,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,33; 86,64</t>
+          <t>-89,12; 79,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,51; 173,73</t>
+          <t>-65,19; 170,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,16; 12,56</t>
+          <t>-79,33; 2,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,21; 19,61</t>
+          <t>-77,12; 19,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 74,47</t>
+          <t>-46,77; 78,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 2,0</t>
+          <t>-8,67; 2,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 1,04</t>
+          <t>-9,22; 1,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 4,8</t>
+          <t>-6,83; 5,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 4,51</t>
+          <t>-6,11; 3,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,44</t>
+          <t>-6,07; 3,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 4,63</t>
+          <t>-5,38; 4,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 2,04</t>
+          <t>-5,67; 1,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,27</t>
+          <t>-5,46; 1,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,95</t>
+          <t>-4,5; 3,41</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-91,22; 103,38</t>
+          <t>-89,43; 119,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-91,85; 77,88</t>
+          <t>-91,44; 80,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,96; 163,3</t>
+          <t>-71,78; 207,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,12; 386,55</t>
+          <t>-87,07; 264,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,0; 255,39</t>
+          <t>-86,81; 234,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,61; 365,32</t>
+          <t>-83,15; 331,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,51; 78,72</t>
+          <t>-75,95; 56,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,49; 46,3</t>
+          <t>-76,45; 55,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 134,81</t>
+          <t>-63,81; 114,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 0,65</t>
+          <t>-10,89; 1,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 8,35</t>
+          <t>-7,36; 8,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 9,66</t>
+          <t>-6,23; 10,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 3,28</t>
+          <t>-6,39; 3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 7,1</t>
+          <t>-4,78; 6,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 5,55</t>
+          <t>-6,15; 6,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 0,81</t>
+          <t>-6,81; 0,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,43</t>
+          <t>-3,59; 6,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 4,71</t>
+          <t>-4,44; 5,3</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,94</t>
+          <t>-100,0; 120,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,56; 348,89</t>
+          <t>-74,93; 342,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,54; 325,76</t>
+          <t>-74,53; 438,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,93; 122,17</t>
+          <t>-82,61; 122,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,98; 257,47</t>
+          <t>-66,59; 223,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,52; 239,81</t>
+          <t>-82,94; 230,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,73; 28,03</t>
+          <t>-78,43; 26,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 147,21</t>
+          <t>-44,69; 141,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 126,68</t>
+          <t>-60,01; 132,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,02</t>
+          <t>-2,82; 5,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,96</t>
+          <t>-3,46; 4,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,67</t>
+          <t>-4,09; 3,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 4,3</t>
+          <t>-3,58; 4,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,64</t>
+          <t>-3,5; 4,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 2,23</t>
+          <t>-5,59; 2,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,22</t>
+          <t>-2,84; 3,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,08</t>
+          <t>-2,26; 2,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,89</t>
+          <t>-3,63; 2,01</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 134,61</t>
+          <t>-40,61; 146,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 106,9</t>
+          <t>-48,51; 110,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,38; 97,68</t>
+          <t>-52,98; 103,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,41; 97,92</t>
+          <t>-44,37; 103,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 106,16</t>
+          <t>-42,8; 114,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,62; 57,39</t>
+          <t>-67,53; 64,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 68,03</t>
+          <t>-39,41; 65,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 66,54</t>
+          <t>-31,61; 67,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 41,88</t>
+          <t>-49,57; 41,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 8,46</t>
+          <t>-3,48; 8,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 7,24</t>
+          <t>-4,73; 6,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 3,76</t>
+          <t>-7,57; 3,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 7,52</t>
+          <t>-5,23; 7,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -2,17</t>
+          <t>-12,25; -2,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,76; -3,12</t>
+          <t>-13,05; -2,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 5,63</t>
+          <t>-2,93; 6,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,76</t>
+          <t>-6,63; 1,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -1,59</t>
+          <t>-8,88; -1,43</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 190,2</t>
+          <t>-31,76; 198,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 169,77</t>
+          <t>-47,35; 161,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,85; 86,26</t>
+          <t>-73,75; 100,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,41; 103,05</t>
+          <t>-38,94; 96,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-88,84; -20,43</t>
+          <t>-88,46; -14,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-91,48; -20,56</t>
+          <t>-91,59; -19,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 82,86</t>
+          <t>-25,7; 90,0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 11,61</t>
+          <t>-58,29; 14,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,65; -19,66</t>
+          <t>-78,57; -14,37</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 2,34</t>
+          <t>-9,52; 2,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 9,45</t>
+          <t>-5,46; 9,72</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 6,16</t>
+          <t>-8,78; 6,72</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 8,41</t>
+          <t>-6,06; 8,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 2,46</t>
+          <t>-9,55; 3,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 6,32</t>
+          <t>-7,75; 6,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 3,84</t>
+          <t>-6,17; 3,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 3,88</t>
+          <t>-6,2; 3,58</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 3,34</t>
+          <t>-6,84; 3,7</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 176,31</t>
+          <t>-100,0; 121,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,9; 301,31</t>
+          <t>-64,97; 281,94</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 486,28</t>
+          <t>-100,0; 341,27</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 232,09</t>
+          <t>-64,31; 275,01</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,48</t>
+          <t>-100,0; 102,11</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-84,76; 220,6</t>
+          <t>-83,49; 212,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 91,09</t>
+          <t>-65,31; 97,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-67,02; 94,17</t>
+          <t>-66,55; 87,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-78,53; 103,48</t>
+          <t>-77,67; 104,6</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,12</t>
+          <t>-3,27; 1,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,69</t>
+          <t>-2,71; 1,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,66</t>
+          <t>-3,03; 1,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,18</t>
+          <t>-2,55; 2,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,09</t>
+          <t>-4,02; -0,02</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,19</t>
+          <t>-4,52; -0,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,96</t>
+          <t>-2,24; 0,93</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,26</t>
+          <t>-2,73; 0,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,1</t>
+          <t>-3,14; 0,1</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 21,79</t>
+          <t>-42,63; 24,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 30,37</t>
+          <t>-34,27; 39,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 29,27</t>
+          <t>-38,42; 31,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 37,63</t>
+          <t>-31,23; 38,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 1,73</t>
+          <t>-51,23; -0,04</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-54,96; 0,25</t>
+          <t>-56,65; -2,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 15,59</t>
+          <t>-28,77; 15,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 4,17</t>
+          <t>-35,84; 6,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 1,52</t>
+          <t>-40,49; 2,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -1,12</t>
+          <t>-12,56; -1,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 3,78</t>
+          <t>-9,86; 3,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 5,82</t>
+          <t>-6,94; 6,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,59</t>
+          <t>-7,41; 3,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 1,54</t>
+          <t>-9,38; 1,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 5,65</t>
+          <t>-5,45; 5,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,1</t>
+          <t>-8,11; -0,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 0,67</t>
+          <t>-7,5; 0,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 3,89</t>
+          <t>-4,74; 4,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -3,94</t>
+          <t>-94,72; 19,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,56; 77,59</t>
+          <t>-78,83; 86,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,28; 100,1</t>
+          <t>-56,2; 114,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,0; 136,6</t>
+          <t>-82,63; 119,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,12; 79,55</t>
+          <t>-89,03; 93,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 170,46</t>
+          <t>-61,58; 180,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,33; 2,27</t>
+          <t>-79,9; -4,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,12; 19,13</t>
+          <t>-75,8; 27,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-46,77; 78,7</t>
+          <t>-48,42; 86,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 2,23</t>
+          <t>-8,6; 2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 1,37</t>
+          <t>-8,53; 1,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 5,35</t>
+          <t>-5,97; 5,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 3,97</t>
+          <t>-5,08; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 3,26</t>
+          <t>-5,41; 3,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,57</t>
+          <t>-4,99; 4,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 1,76</t>
+          <t>-5,57; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,16</t>
+          <t>-5,65; 1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,41</t>
+          <t>-4,3; 3,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-89,43; 119,02</t>
+          <t>-88,7; 135,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-91,44; 80,26</t>
+          <t>-89,32; 99,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,78; 207,7</t>
+          <t>-67,71; 194,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,07; 264,07</t>
+          <t>-82,91; 343,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,81; 234,18</t>
+          <t>-82,33; 212,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,15; 331,02</t>
+          <t>-79,7; 376,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,95; 56,1</t>
+          <t>-74,47; 56,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,45; 55,61</t>
+          <t>-76,41; 46,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 114,2</t>
+          <t>-63,81; 124,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 1,17</t>
+          <t>-10,88; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 8,32</t>
+          <t>-6,66; 8,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 10,67</t>
+          <t>-6,93; 9,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 3,48</t>
+          <t>-6,82; 3,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 6,99</t>
+          <t>-4,15; 7,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 6,04</t>
+          <t>-6,27; 6,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 0,69</t>
+          <t>-7,08; 0,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 6,16</t>
+          <t>-3,85; 5,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 5,3</t>
+          <t>-4,59; 5,22</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,5</t>
+          <t>-100,0; 93,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,93; 342,93</t>
+          <t>-78,52; 277,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,53; 438,87</t>
+          <t>-78,65; 301,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,61; 122,69</t>
+          <t>-80,47; 152,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,59; 223,22</t>
+          <t>-58,4; 272,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,94; 230,26</t>
+          <t>-83,24; 231,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,43; 26,51</t>
+          <t>-79,31; 39,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 141,76</t>
+          <t>-49,38; 139,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,01; 132,91</t>
+          <t>-62,61; 141,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 5,29</t>
+          <t>-2,81; 4,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 4,15</t>
+          <t>-3,11; 4,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 3,84</t>
+          <t>-3,89; 3,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 4,55</t>
+          <t>-4,21; 4,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 4,86</t>
+          <t>-3,86; 4,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,46</t>
+          <t>-5,55; 2,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,06</t>
+          <t>-2,44; 3,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,98</t>
+          <t>-2,79; 3,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,01</t>
+          <t>-3,78; 1,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 146,93</t>
+          <t>-40,36; 140,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,51; 110,77</t>
+          <t>-44,54; 121,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 103,3</t>
+          <t>-53,21; 110,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 103,5</t>
+          <t>-50,37; 92,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 114,51</t>
+          <t>-47,94; 102,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,53; 64,06</t>
+          <t>-64,67; 72,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 65,87</t>
+          <t>-33,06; 69,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 67,13</t>
+          <t>-39,2; 61,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 41,02</t>
+          <t>-51,13; 41,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 8,72</t>
+          <t>-2,68; 9,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 6,92</t>
+          <t>-4,36; 7,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 3,6</t>
+          <t>-7,88; 3,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 7,32</t>
+          <t>-5,72; 6,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -2,09</t>
+          <t>-13,05; -1,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,05; -2,86</t>
+          <t>-13,21; -3,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 6,26</t>
+          <t>-2,78; 6,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 1,02</t>
+          <t>-6,94; 0,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -1,43</t>
+          <t>-9,27; -1,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 198,71</t>
+          <t>-27,78; 213,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 161,63</t>
+          <t>-43,59; 170,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 100,09</t>
+          <t>-78,52; 85,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 96,66</t>
+          <t>-43,06; 87,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-88,46; -14,68</t>
+          <t>-88,32; -18,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-91,59; -19,16</t>
+          <t>-92,92; -23,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 90,0</t>
+          <t>-24,69; 92,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 14,94</t>
+          <t>-60,06; 18,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-78,57; -14,37</t>
+          <t>-80,39; -16,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 2,36</t>
+          <t>-9,64; 2,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 9,72</t>
+          <t>-5,92; 9,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 6,72</t>
+          <t>-8,51; 7,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 8,47</t>
+          <t>-6,74; 8,29</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 3,01</t>
+          <t>-9,46; 2,57</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 6,19</t>
+          <t>-8,7; 6,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 3,96</t>
+          <t>-5,64; 4,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 3,58</t>
+          <t>-6,19; 3,6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 3,7</t>
+          <t>-6,91; 3,26</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,16</t>
+          <t>-100,0; 122,94</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-64,97; 281,94</t>
+          <t>-68,18; 306,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 341,27</t>
+          <t>-100,0; 446,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 275,01</t>
+          <t>-71,86; 250,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,11</t>
+          <t>-98,65; 114,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-83,49; 212,04</t>
+          <t>-84,55; 242,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 97,03</t>
+          <t>-66,65; 105,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 87,72</t>
+          <t>-67,51; 92,37</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-77,67; 104,6</t>
+          <t>-79,23; 92,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,3</t>
+          <t>-3,32; 1,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,96</t>
+          <t>-2,64; 2,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,67</t>
+          <t>-3,16; 1,65</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,04</t>
+          <t>-2,62; 1,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -0,02</t>
+          <t>-4,01; 0,31</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,3</t>
+          <t>-4,39; -0,11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,93</t>
+          <t>-2,27; 1,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,38</t>
+          <t>-2,88; 0,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,1</t>
+          <t>-3,23; -0,02</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 24,94</t>
+          <t>-42,16; 17,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 39,57</t>
+          <t>-33,84; 37,3</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 31,7</t>
+          <t>-39,96; 29,46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-31,23; 38,15</t>
+          <t>-32,77; 32,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-51,23; -0,04</t>
+          <t>-49,33; 7,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-56,65; -2,85</t>
+          <t>-54,76; -1,47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 15,83</t>
+          <t>-29,27; 17,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 6,42</t>
+          <t>-37,68; 7,43</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 2,54</t>
+          <t>-41,98; -0,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,34</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -1,25</t>
+          <t>-6,74; 3,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 3,28</t>
+          <t>-8,23; 1,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 6,11</t>
+          <t>-5,57; 5,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 3,6</t>
+          <t>-12,38; -1,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 1,52</t>
+          <t>-9,85; 3,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 5,7</t>
+          <t>-6,94; 6,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -0,35</t>
+          <t>-8,14; -0,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,99</t>
+          <t>-7,98; 0,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 4,3</t>
+          <t>-4,61; 4,17</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-27,91%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-52,61%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-72,32%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-36,5%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,19%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-27,91%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-52,61%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-2,31%</t>
+          <t>-1,03%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-94,72; 19,93</t>
+          <t>-77,57; 138,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,83; 86,81</t>
+          <t>-88,33; 86,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,2; 114,58</t>
+          <t>-62,0; 171,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,63; 119,06</t>
+          <t>-94,19; -7,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,03; 93,58</t>
+          <t>-80,73; 75,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 180,54</t>
+          <t>-55,94; 124,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,9; -4,89</t>
+          <t>-79,16; 12,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 27,18</t>
+          <t>-76,21; 19,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 86,11</t>
+          <t>-45,24; 80,21</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,68</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,42</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 2,48</t>
+          <t>-5,05; 4,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 1,55</t>
+          <t>-5,55; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 5,5</t>
+          <t>-5,62; 3,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 4,21</t>
+          <t>-9,23; 2,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 3,2</t>
+          <t>-9,83; 1,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 4,77</t>
+          <t>-7,86; 4,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 1,74</t>
+          <t>-5,39; 2,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,11</t>
+          <t>-5,76; 1,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,58</t>
+          <t>-4,2; 3,47</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-9,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-16,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-18,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-47,21%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-55,63%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-10,98%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-9,17%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-16,77%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,19%</t>
+          <t>-12,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,16%</t>
+          <t>-13,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-88,7; 135,8</t>
+          <t>-76,12; 386,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-89,32; 99,23</t>
+          <t>-83,0; 255,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 194,82</t>
+          <t>-89,31; 317,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,91; 343,02</t>
+          <t>-91,22; 103,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,33; 212,01</t>
+          <t>-91,85; 77,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,7; 376,85</t>
+          <t>-78,57; 156,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,47; 56,11</t>
+          <t>-75,51; 78,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,41; 46,78</t>
+          <t>-77,49; 46,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 124,1</t>
+          <t>-62,54; 121,09</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,94</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,87</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,05</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,43</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 0,94</t>
+          <t>-6,74; 3,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 8,08</t>
+          <t>-4,76; 7,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 9,71</t>
+          <t>-6,51; 5,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 3,85</t>
+          <t>-10,77; 0,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 7,65</t>
+          <t>-5,77; 8,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 6,36</t>
+          <t>-6,61; 9,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 0,84</t>
+          <t>-6,66; 0,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 5,55</t>
+          <t>-4,24; 5,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 5,22</t>
+          <t>-4,53; 5,2</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-29,52%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16,56%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-15,19%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-61,76%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14,97%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-29,52%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,56%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-17,22%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-1,26%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 93,09</t>
+          <t>-82,93; 122,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,52; 277,93</t>
+          <t>-62,98; 257,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,65; 301,74</t>
+          <t>-83,01; 240,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,47; 152,53</t>
+          <t>-100,0; 61,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,4; 272,44</t>
+          <t>-66,56; 348,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,24; 231,12</t>
+          <t>-76,55; 323,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,31; 39,02</t>
+          <t>-78,73; 28,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 139,32</t>
+          <t>-50,22; 147,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,61; 141,18</t>
+          <t>-61,1; 131,85</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,92</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 4,88</t>
+          <t>-3,87; 4,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,14</t>
+          <t>-3,8; 4,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,95</t>
+          <t>-5,43; 2,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 4,09</t>
+          <t>-2,92; 5,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 4,34</t>
+          <t>-3,42; 3,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 2,58</t>
+          <t>-2,5; 5,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,39</t>
+          <t>-2,27; 3,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,03</t>
+          <t>-2,39; 3,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 1,68</t>
+          <t>-3,02; 2,63</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-26,62%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>16,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0,17%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-26,75%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,41%</t>
+          <t>-3,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 140,86</t>
+          <t>-47,41; 97,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 121,32</t>
+          <t>-42,85; 106,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 110,57</t>
+          <t>-67,36; 60,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,37; 92,49</t>
+          <t>-42,79; 134,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 102,87</t>
+          <t>-47,34; 106,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 72,78</t>
+          <t>-37,1; 149,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 69,84</t>
+          <t>-32,37; 68,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 61,37</t>
+          <t>-33,75; 66,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 41,03</t>
+          <t>-43,18; 57,43</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,71</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-7,03</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-7,88</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,99</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-7,03</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,03</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,34</t>
+          <t>-5,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 9,12</t>
+          <t>-5,79; 7,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 7,76</t>
+          <t>-12,56; -2,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,45</t>
+          <t>-13,5; -2,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 6,9</t>
+          <t>-3,02; 8,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,05; -1,92</t>
+          <t>-4,52; 7,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -3,23</t>
+          <t>-7,85; 4,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 6,48</t>
+          <t>-2,87; 5,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 0,8</t>
+          <t>-7,59; 0,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -1,58</t>
+          <t>-9,07; -1,25</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-65,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-72,87%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>41,28%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>22,91%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-26,38%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-65,0%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-74,2%</t>
+          <t>-24,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-57,99%</t>
+          <t>-55,76%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 213,35</t>
+          <t>-41,41; 103,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 170,85</t>
+          <t>-88,84; -20,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,52; 85,49</t>
+          <t>-91,58; -18,94</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 87,5</t>
+          <t>-30,53; 190,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-88,32; -18,02</t>
+          <t>-45,89; 169,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-92,92; -23,03</t>
+          <t>-74,99; 95,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 92,83</t>
+          <t>-26,07; 82,86</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,06; 18,54</t>
+          <t>-65,27; 11,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,39; -16,67</t>
+          <t>-79,99; -14,89</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-3,48</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-3,68</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,28</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,86</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-3,48</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-5,05</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-3,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 2,61</t>
+          <t>-6,02; 8,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 9,68</t>
+          <t>-10,52; 2,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 7,52</t>
+          <t>-8,73; 5,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 8,29</t>
+          <t>-9,97; 2,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 2,57</t>
+          <t>-5,32; 9,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 6,3</t>
+          <t>-11,33; -1,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 4,45</t>
+          <t>-5,8; 3,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 3,6</t>
+          <t>-5,6; 3,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 3,26</t>
+          <t>-7,76; 0,6</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>10,8%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-49,93%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-25,4%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-58,07%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>20,16%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-45,12%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-49,93%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-22,37%</t>
+          <t>-79,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-32,92%</t>
+          <t>-51,88%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 122,94</t>
+          <t>-64,29; 232,09</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,18; 306,87</t>
+          <t>-100,0; 110,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 446,28</t>
+          <t>-85,6; 206,46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-71,86; 250,87</t>
+          <t>-100,0; 176,31</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-98,65; 114,46</t>
+          <t>-68,9; 301,31</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-84,55; 242,18</t>
+          <t>-100,0; 32,48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-66,65; 105,32</t>
+          <t>-65,11; 91,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-67,51; 92,37</t>
+          <t>-67,02; 94,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-79,23; 92,69</t>
+          <t>-83,37; 38,53</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-2,06</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-2,37</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,14</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,42</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-2,06</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,55</t>
+          <t>-1,46</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,0</t>
+          <t>-2,38; 2,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,15</t>
+          <t>-4,21; 0,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,65</t>
+          <t>-4,54; -0,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,94</t>
+          <t>-3,23; 1,12</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,31</t>
+          <t>-2,63; 1,69</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,11</t>
+          <t>-2,76; 1,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,03</t>
+          <t>-2,34; 0,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,38</t>
+          <t>-2,82; 0,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,02</t>
+          <t>-3,14; 0,23</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-2,71%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-29,94%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-34,48%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-17,19%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-6,34%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-10,57%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-2,71%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-29,94%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-33,59%</t>
+          <t>-6,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-22,98%</t>
+          <t>-21,65%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 17,72</t>
+          <t>-31,18; 37,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 37,3</t>
+          <t>-53,17; 1,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 29,46</t>
+          <t>-56,19; -1,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 32,64</t>
+          <t>-41,57; 21,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 7,79</t>
+          <t>-34,4; 30,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-54,76; -1,47</t>
+          <t>-34,99; 31,79</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 17,92</t>
+          <t>-30,76; 15,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 7,43</t>
+          <t>-36,85; 4,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-41,98; -0,08</t>
+          <t>-42,21; 3,48</t>
         </is>
       </c>
     </row>
